--- a/outputs/493-5.xlsx
+++ b/outputs/493-5.xlsx
@@ -145,24 +145,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -358,175 +362,175 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>624515</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43840</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>1736.522</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <f aca="false">+C2-D2</f>
         <v>-1736.522</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>2060</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <f aca="false">+C3-D3</f>
         <v>-2060</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>624516</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1855.652</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <f aca="false">+C4-D4</f>
         <v>-1855.652</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>624519</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43841</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1960.87</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <f aca="false">+C5-D5</f>
         <v>-1960.87</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>624521</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43842</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="n">
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1348.6</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <f aca="false">+C6-D6</f>
         <v>-1348.6</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>624527</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>1399.024</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <f aca="false">+C9-D9</f>
         <v>0</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>1820</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <f aca="false">+C10-D10</f>
         <v>0</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>15</v>
       </c>
     </row>

--- a/outputs/493-5.xlsx
+++ b/outputs/493-5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t xml:space="preserve">Reference</t>
   </si>
@@ -359,7 +359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.57"/>
@@ -494,43 +494,64 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
+        <v>624521</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>43842</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <f aca="false">+C7-D7</f>
+        <v>-1348.6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>624527</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>1399.024</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <f aca="false">+C9-D9</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="s">
+        <v>-1820</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>1820</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <f aca="false">+C10-D10</f>
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
